--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-12.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_6405B28954FABB4DC39B3211595ED87656CD4A47" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE7AFF9A-5086-4114-919F-5DF9967A556B}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="11_6405B28954FABB4DC39B3211595ED87656CD4A47" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19133D7E-E825-4D5A-82C1-DBE5916E256D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -629,6 +629,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -918,6 +922,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="18.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-12.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-12.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,12 +595,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -674,12 +674,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -753,12 +753,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -990,12 +990,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>4x2</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0x6</t>
+          <t>0-6</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1780,12 +1780,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0x3</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2183,12 +2183,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1x5</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2262,12 +2262,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2428,12 +2428,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2592,12 +2592,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>5x0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -2671,12 +2671,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2829,12 +2829,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -2908,12 +2908,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>5x0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -2987,12 +2987,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>6x1</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -3066,12 +3066,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-12.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-12.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,12 +595,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -674,12 +674,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>2x5</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -753,12 +753,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -990,12 +990,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4x2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0-6</t>
+          <t>0x6</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1780,12 +1780,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0x3</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2183,12 +2183,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>1x5</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2262,12 +2262,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2428,12 +2428,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2592,12 +2592,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>5x0</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -2671,12 +2671,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2829,12 +2829,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -2908,12 +2908,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>5x0</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -2987,12 +2987,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>6x1</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -3066,12 +3066,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-12.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-12.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2428,19 +2428,19 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S25" t="n">
